--- a/hardware/v2/BOM_4层非开发板版本_openups.xlsx
+++ b/hardware/v2/BOM_4层非开发板版本_openups.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-13" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="404">
   <si>
     <t>Quantity</t>
   </si>
@@ -112,639 +112,645 @@
     <t>贴片电容(MLCC)</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>C1,C2,C3,C4,C12,C13,C14,C18,C19,C20,C26,C27,C28,C29,C30,C31,C32,C33,C41,C43,C44,C45,C47</t>
+    <t>24</t>
+  </si>
+  <si>
+    <t>C1,C2,C3,C4,C12,C13,C14,C18,C19,C20,C26,C27,C28,C29,C30,C31,C32,C33,C41,C43,C44,C45,C47,C48</t>
   </si>
   <si>
     <t>100nF</t>
   </si>
   <si>
-    <t>FCC0603B104K500CT</t>
+    <t>CGA0603X7R104K500JT,FCC0603B104K500CT</t>
+  </si>
+  <si>
+    <t>FOJAN(富捷),HRE(芯声)</t>
+  </si>
+  <si>
+    <t>C5137636,C6119867</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>C5,C6,C34,C36,C37</t>
+  </si>
+  <si>
+    <t>1uF</t>
+  </si>
+  <si>
+    <t>CGA0603X5R105K500JT</t>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+  </si>
+  <si>
+    <t>C6119852</t>
+  </si>
+  <si>
+    <t>C7,C16</t>
+  </si>
+  <si>
+    <t>47nF</t>
+  </si>
+  <si>
+    <t>CL10B473KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1622</t>
+  </si>
+  <si>
+    <t>C8,C9,C24,C25,C46</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>CGA0603X5R106K100JT,CL10A106MA8NRNC</t>
+  </si>
+  <si>
+    <t>HRE(芯声),SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C96446,C6119842</t>
+  </si>
+  <si>
+    <t>C10,C11,C15,C38,C40</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>CL10C101JB8NNNC</t>
+  </si>
+  <si>
+    <t>C14858</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>1nF</t>
+  </si>
+  <si>
+    <t>CL10B102KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1588</t>
+  </si>
+  <si>
+    <t>C21,C22</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>CL10A226MP8NUNE</t>
+  </si>
+  <si>
+    <t>C86295</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>33pF</t>
+  </si>
+  <si>
+    <t>CL10C330JB8NNNC</t>
+  </si>
+  <si>
+    <t>C1663</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>CGA0603X5R475K250JT</t>
+  </si>
+  <si>
+    <t>C6119856</t>
+  </si>
+  <si>
+    <t>C39,C42</t>
+  </si>
+  <si>
+    <t>10nF</t>
+  </si>
+  <si>
+    <t>CL10B103KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1589</t>
+  </si>
+  <si>
+    <t>CN1</t>
+  </si>
+  <si>
+    <t>CONN-TH_6P-P2.50_HCZZ0139-6</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>HX-XH2.54-6PWZ</t>
+  </si>
+  <si>
+    <t>hanxia(韩下)</t>
+  </si>
+  <si>
+    <t>C48641718</t>
+  </si>
+  <si>
+    <t>连接器</t>
+  </si>
+  <si>
+    <t>线对板针座</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>CN2,CN6</t>
+  </si>
+  <si>
+    <t>CONN-TH_HX-XH2.54-2PWZ</t>
+  </si>
+  <si>
+    <t>HX-XH2.54-2PWZ</t>
+  </si>
+  <si>
+    <t>C48641714</t>
+  </si>
+  <si>
+    <t>CN3</t>
+  </si>
+  <si>
+    <t>CONN-TH_XT30PW-M</t>
+  </si>
+  <si>
+    <t>XT30PW-M30.G.Y</t>
+  </si>
+  <si>
+    <t>AMASS(艾迈斯)</t>
+  </si>
+  <si>
+    <t>C431092</t>
+  </si>
+  <si>
+    <t>工控电气</t>
+  </si>
+  <si>
+    <t>插头</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>CN4</t>
+  </si>
+  <si>
+    <t>CONN-SMD_4P-P1.00_WAFER-SH1.0-4PWB</t>
+  </si>
+  <si>
+    <t>WAFER-SH1.0-4PWB</t>
+  </si>
+  <si>
+    <t>XUNPU(讯普)</t>
+  </si>
+  <si>
+    <t>C3029343</t>
+  </si>
+  <si>
+    <t>Csys</t>
+  </si>
+  <si>
+    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.3-FD-H7.7</t>
+  </si>
+  <si>
+    <t>220uF</t>
+  </si>
+  <si>
+    <t>JVJ25V220M6x8</t>
+  </si>
+  <si>
+    <t>JIERR(捷而瑞)</t>
+  </si>
+  <si>
+    <t>C46550404</t>
+  </si>
+  <si>
+    <t>贴片型铝电解电容</t>
+  </si>
+  <si>
+    <t>D1</t>
+  </si>
+  <si>
+    <t>SOD-123FL_L2.7-W1.8-LS3.8-RD</t>
+  </si>
+  <si>
+    <t>SMF24A</t>
+  </si>
+  <si>
+    <t>SMF24A_C19077514</t>
+  </si>
+  <si>
+    <t>R+O(宏嘉诚)</t>
+  </si>
+  <si>
+    <t>C19077514</t>
+  </si>
+  <si>
+    <t>三极管/MOS管/晶体管</t>
+  </si>
+  <si>
+    <t>静电和浪涌保护(TVS/ESD)</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
+  </si>
+  <si>
+    <t>BAT54C,215</t>
+  </si>
+  <si>
+    <t>Nexperia(安世)</t>
+  </si>
+  <si>
+    <t>C37704</t>
+  </si>
+  <si>
+    <t>二极管</t>
+  </si>
+  <si>
+    <t>肖特基二极管</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>D3,D4</t>
+  </si>
+  <si>
+    <t>SOD-323_L1.7-W1.3-LS2.6-RD-1</t>
+  </si>
+  <si>
+    <t>BAT54WS</t>
+  </si>
+  <si>
+    <t>BAT54WS_C7502694</t>
+  </si>
+  <si>
+    <t>C7502694</t>
+  </si>
+  <si>
+    <t>DC1</t>
+  </si>
+  <si>
+    <t>DC-IN-TH_HC-DC-007B-2.5</t>
+  </si>
+  <si>
+    <t>HC-DC-007B-2.5</t>
+  </si>
+  <si>
+    <t>HCTL(华灿天禄)</t>
+  </si>
+  <si>
+    <t>C3010538</t>
+  </si>
+  <si>
+    <t>DC电源连接器</t>
+  </si>
+  <si>
+    <t>DCout</t>
+  </si>
+  <si>
+    <t>CONN-TH_XT30PW-F-1</t>
+  </si>
+  <si>
+    <t>XT30PW-F20.G.Y</t>
+  </si>
+  <si>
+    <t>C2913282</t>
+  </si>
+  <si>
+    <t>电源连接器/插接器</t>
+  </si>
+  <si>
+    <t>H1</t>
+  </si>
+  <si>
+    <t>HDR-TH_4P-P2.54-V-M</t>
+  </si>
+  <si>
+    <t>PZ254V-11-04P</t>
+  </si>
+  <si>
+    <t>XFCN(兴飞)</t>
+  </si>
+  <si>
+    <t>C2691448</t>
+  </si>
+  <si>
+    <t>排针</t>
+  </si>
+  <si>
+    <t>L1</t>
+  </si>
+  <si>
+    <t>IND-SMD_L5.4-W5.2_FXL05XX</t>
+  </si>
+  <si>
+    <t>3.3uH</t>
+  </si>
+  <si>
+    <t>FXL0530-3R3-M</t>
+  </si>
+  <si>
+    <t>cjiang(长江微电)</t>
+  </si>
+  <si>
+    <t>C475518</t>
+  </si>
+  <si>
+    <t>电感/线圈/变压器</t>
+  </si>
+  <si>
+    <t>功率电感</t>
+  </si>
+  <si>
+    <t>L2</t>
+  </si>
+  <si>
+    <t>IND-SMD_L5.4-W5.2_FXL0530</t>
+  </si>
+  <si>
+    <t>4.7uH</t>
+  </si>
+  <si>
+    <t>FXL0530-4R7-M</t>
+  </si>
+  <si>
+    <t>C177246</t>
+  </si>
+  <si>
+    <t>LED1</t>
+  </si>
+  <si>
+    <t>LED0603-RD</t>
+  </si>
+  <si>
+    <t>GL0603UG01</t>
+  </si>
+  <si>
+    <t>Guiguang light(桂光光电)</t>
+  </si>
+  <si>
+    <t>C51933293</t>
+  </si>
+  <si>
+    <t>光电器件</t>
+  </si>
+  <si>
+    <t>发光二极管/LED</t>
+  </si>
+  <si>
+    <t>LED2</t>
+  </si>
+  <si>
+    <t>LED0603-FD</t>
+  </si>
+  <si>
+    <t>GL0603UR01</t>
+  </si>
+  <si>
+    <t>C51933292</t>
+  </si>
+  <si>
+    <t>LED3</t>
+  </si>
+  <si>
+    <t>LED0603-RD_BLUE</t>
+  </si>
+  <si>
+    <t>GL0603UB01</t>
+  </si>
+  <si>
+    <t>C51933294</t>
+  </si>
+  <si>
+    <t>LED4</t>
+  </si>
+  <si>
+    <t>LED-SMD_4P-L1.6-W0.8-RD_1</t>
+  </si>
+  <si>
+    <t>XL-1608SURUGC</t>
+  </si>
+  <si>
+    <t>XINGLIGHT(成兴光)</t>
+  </si>
+  <si>
+    <t>C5349934</t>
+  </si>
+  <si>
+    <t>Q1,Q2,Q6</t>
+  </si>
+  <si>
+    <t>SOP-8_L5.0-W4.0-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
+    <t>FDS6680A</t>
+  </si>
+  <si>
+    <t>onsemi(安森美)</t>
+  </si>
+  <si>
+    <t>C87668</t>
+  </si>
+  <si>
+    <t>场效应管(MOSFET)</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Q3,Q4,Q7,Q8</t>
+  </si>
+  <si>
+    <t>PDFN-8_L3.1-W3.1-P0.65-LS3.4-BL</t>
+  </si>
+  <si>
+    <t>SIS412DN-T1-GE3-ES</t>
+  </si>
+  <si>
+    <t>ElecSuper(静芯)</t>
+  </si>
+  <si>
+    <t>C21713860</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>SC-70-3_L2.0-W1.3-P0.65-LS2.1-BL</t>
+  </si>
+  <si>
+    <t>BSS138W</t>
+  </si>
+  <si>
+    <t>BSS138W_C890266</t>
+  </si>
+  <si>
+    <t>C890266</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR-1</t>
+  </si>
+  <si>
+    <t>BSS84</t>
+  </si>
+  <si>
+    <t>BSS84_C7420340</t>
+  </si>
+  <si>
+    <t>C7420340</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
+  </si>
+  <si>
+    <t>AO3401</t>
+  </si>
+  <si>
+    <t>AO3401_C5224195</t>
+  </si>
+  <si>
+    <t>C5224195</t>
+  </si>
+  <si>
+    <t>R0</t>
+  </si>
+  <si>
+    <t>R0603</t>
+  </si>
+  <si>
+    <t>2Ω</t>
+  </si>
+  <si>
+    <t>0603WAF200KT5E</t>
+  </si>
+  <si>
+    <t>UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C22977</t>
+  </si>
+  <si>
+    <t>电阻</t>
+  </si>
+  <si>
+    <t>贴片电阻</t>
+  </si>
+  <si>
+    <t>R1,R18</t>
+  </si>
+  <si>
+    <t>499kΩ</t>
+  </si>
+  <si>
+    <t>0603WAF4993T5E</t>
+  </si>
+  <si>
+    <t>C26751</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>133kΩ</t>
+  </si>
+  <si>
+    <t>0603WAF1333T5E</t>
+  </si>
+  <si>
+    <t>C22870</t>
+  </si>
+  <si>
+    <t>R3,R9,R14,R15,R20,R42</t>
+  </si>
+  <si>
+    <t>10Ω</t>
+  </si>
+  <si>
+    <t>0603WAF100JT5E</t>
+  </si>
+  <si>
+    <t>C22859</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>316kΩ</t>
+  </si>
+  <si>
+    <t>0603WAF3163T5E</t>
+  </si>
+  <si>
+    <t>C25814</t>
+  </si>
+  <si>
+    <t>R5,R44,R48</t>
+  </si>
+  <si>
+    <t>100kΩ</t>
+  </si>
+  <si>
+    <t>0603WAF1003T5E</t>
+  </si>
+  <si>
+    <t>C25803</t>
+  </si>
+  <si>
+    <t>R6,R10,R11,R55,R67</t>
+  </si>
+  <si>
+    <t>4.7kΩ</t>
+  </si>
+  <si>
+    <t>0603WAF4701T5E</t>
+  </si>
+  <si>
+    <t>C23162</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>14.3kΩ</t>
+  </si>
+  <si>
+    <t>FRC0603F1432TS</t>
   </si>
   <si>
     <t>FOJAN(富捷)</t>
   </si>
   <si>
-    <t>C5137636</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>C5,C6,C34,C36,C37</t>
-  </si>
-  <si>
-    <t>1uF</t>
-  </si>
-  <si>
-    <t>CGA0603X5R105K500JT</t>
-  </si>
-  <si>
-    <t>HRE(芯声)</t>
-  </si>
-  <si>
-    <t>C6119852</t>
-  </si>
-  <si>
-    <t>C7,C16</t>
-  </si>
-  <si>
-    <t>47nF</t>
-  </si>
-  <si>
-    <t>CL10B473KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1622</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>C8,C9,C24,C25,C46,C48</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>CGA0603X5R106K100JT,CL10A106MA8NRNC</t>
-  </si>
-  <si>
-    <t>HRE(芯声),SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>C96446,C6119842</t>
-  </si>
-  <si>
-    <t>C10,C11,C15,C38,C40</t>
-  </si>
-  <si>
-    <t>100pF</t>
-  </si>
-  <si>
-    <t>CL10C101JB8NNNC</t>
-  </si>
-  <si>
-    <t>C14858</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>1nF</t>
-  </si>
-  <si>
-    <t>CL10B102KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1588</t>
-  </si>
-  <si>
-    <t>C21,C22</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>CL10A226MP8NUNE</t>
-  </si>
-  <si>
-    <t>C86295</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>33pF</t>
-  </si>
-  <si>
-    <t>CL10C330JB8NNNC</t>
-  </si>
-  <si>
-    <t>C1663</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>CGA0603X5R475K250JT</t>
-  </si>
-  <si>
-    <t>C6119856</t>
-  </si>
-  <si>
-    <t>C39,C42</t>
-  </si>
-  <si>
-    <t>10nF</t>
-  </si>
-  <si>
-    <t>CL10B103KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1589</t>
-  </si>
-  <si>
-    <t>CN1</t>
-  </si>
-  <si>
-    <t>CONN-TH_6P-P2.50_HCZZ0139-6</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>HX-XH2.54-6PWZ</t>
-  </si>
-  <si>
-    <t>hanxia(韩下)</t>
-  </si>
-  <si>
-    <t>C48641718</t>
-  </si>
-  <si>
-    <t>连接器</t>
-  </si>
-  <si>
-    <t>线对板针座</t>
-  </si>
-  <si>
-    <t>CN2,CN6</t>
-  </si>
-  <si>
-    <t>CONN-TH_HX-XH2.54-2PWZ</t>
-  </si>
-  <si>
-    <t>HX-XH2.54-2PWZ</t>
-  </si>
-  <si>
-    <t>C48641714</t>
-  </si>
-  <si>
-    <t>CN3</t>
-  </si>
-  <si>
-    <t>CONN-TH_XT30PW-M</t>
-  </si>
-  <si>
-    <t>XT30PW-M30.G.Y</t>
-  </si>
-  <si>
-    <t>AMASS(艾迈斯)</t>
-  </si>
-  <si>
-    <t>C431092</t>
-  </si>
-  <si>
-    <t>工控电气</t>
-  </si>
-  <si>
-    <t>插头</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>Csys</t>
-  </si>
-  <si>
-    <t>CAP-SMD_BD6.3-L6.6-W6.6-LS7.3-FD-H7.7</t>
-  </si>
-  <si>
-    <t>220uF</t>
-  </si>
-  <si>
-    <t>JVJ25V220M6x8</t>
-  </si>
-  <si>
-    <t>JIERR(捷而瑞)</t>
-  </si>
-  <si>
-    <t>C46550404</t>
-  </si>
-  <si>
-    <t>贴片型铝电解电容</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
-    <t>SOD-123FL_L2.7-W1.8-LS3.8-RD</t>
-  </si>
-  <si>
-    <t>SMF24A</t>
-  </si>
-  <si>
-    <t>SMF24A_C19077514</t>
-  </si>
-  <si>
-    <t>R+O(宏嘉诚)</t>
-  </si>
-  <si>
-    <t>C19077514</t>
-  </si>
-  <si>
-    <t>三极管/MOS管/晶体管</t>
-  </si>
-  <si>
-    <t>静电和浪涌保护(TVS/ESD)</t>
-  </si>
-  <si>
-    <t>D2</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.6-P1.90-LS2.8-BR</t>
-  </si>
-  <si>
-    <t>BAT54C,215</t>
-  </si>
-  <si>
-    <t>Nexperia(安世)</t>
-  </si>
-  <si>
-    <t>C37704</t>
-  </si>
-  <si>
-    <t>二极管</t>
-  </si>
-  <si>
-    <t>肖特基二极管</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>D3,D4</t>
-  </si>
-  <si>
-    <t>SOD-323_L1.7-W1.3-LS2.6-RD-1</t>
-  </si>
-  <si>
-    <t>BAT54WS</t>
-  </si>
-  <si>
-    <t>BAT54WS_C7502694</t>
-  </si>
-  <si>
-    <t>C7502694</t>
-  </si>
-  <si>
-    <t>DC1</t>
-  </si>
-  <si>
-    <t>DC-IN-TH_HC-DC-007B-2.5</t>
-  </si>
-  <si>
-    <t>HC-DC-007B-2.5</t>
-  </si>
-  <si>
-    <t>HCTL(华灿天禄)</t>
-  </si>
-  <si>
-    <t>C3010538</t>
-  </si>
-  <si>
-    <t>DC电源连接器</t>
-  </si>
-  <si>
-    <t>DCout</t>
-  </si>
-  <si>
-    <t>CONN-TH_XT30PW-F-1</t>
-  </si>
-  <si>
-    <t>XT30PW-F20.G.Y</t>
-  </si>
-  <si>
-    <t>C2913282</t>
-  </si>
-  <si>
-    <t>电源连接器/插接器</t>
-  </si>
-  <si>
-    <t>H1</t>
-  </si>
-  <si>
-    <t>HDR-TH_4P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>PZ254V-11-04P</t>
-  </si>
-  <si>
-    <t>XFCN(兴飞)</t>
-  </si>
-  <si>
-    <t>C2691448</t>
-  </si>
-  <si>
-    <t>排针</t>
-  </si>
-  <si>
-    <t>H2</t>
-  </si>
-  <si>
-    <t>HDR-TH_2P-P2.54-V-M</t>
-  </si>
-  <si>
-    <t>PZ254V-11-02P</t>
-  </si>
-  <si>
-    <t>C492401</t>
-  </si>
-  <si>
-    <t>L1</t>
-  </si>
-  <si>
-    <t>IND-SMD_L5.4-W5.2_FXL05XX</t>
-  </si>
-  <si>
-    <t>3.3uH</t>
-  </si>
-  <si>
-    <t>FXL0530-3R3-M</t>
-  </si>
-  <si>
-    <t>cjiang(长江微电)</t>
-  </si>
-  <si>
-    <t>C475518</t>
-  </si>
-  <si>
-    <t>电感/线圈/变压器</t>
-  </si>
-  <si>
-    <t>功率电感</t>
-  </si>
-  <si>
-    <t>L2</t>
-  </si>
-  <si>
-    <t>IND-SMD_L5.4-W5.2_FXL0530</t>
-  </si>
-  <si>
-    <t>4.7uH</t>
-  </si>
-  <si>
-    <t>FXL0530-4R7-M</t>
-  </si>
-  <si>
-    <t>C177246</t>
-  </si>
-  <si>
-    <t>LED1</t>
-  </si>
-  <si>
-    <t>LED0603-RD</t>
-  </si>
-  <si>
-    <t>GL0603UG01</t>
-  </si>
-  <si>
-    <t>Guiguang light(桂光光电)</t>
-  </si>
-  <si>
-    <t>C51933293</t>
-  </si>
-  <si>
-    <t>光电器件</t>
-  </si>
-  <si>
-    <t>发光二极管/LED</t>
-  </si>
-  <si>
-    <t>LED2</t>
-  </si>
-  <si>
-    <t>LED0603-FD</t>
-  </si>
-  <si>
-    <t>GL0603UR01</t>
-  </si>
-  <si>
-    <t>C51933292</t>
-  </si>
-  <si>
-    <t>LED3</t>
-  </si>
-  <si>
-    <t>LED0603-RD_BLUE</t>
-  </si>
-  <si>
-    <t>GL0603UB01</t>
-  </si>
-  <si>
-    <t>C51933294</t>
-  </si>
-  <si>
-    <t>LED4</t>
-  </si>
-  <si>
-    <t>LED-SMD_4P-L1.6-W0.8-RD_1</t>
-  </si>
-  <si>
-    <t>XL-1608SURUGC</t>
-  </si>
-  <si>
-    <t>XINGLIGHT(成兴光)</t>
-  </si>
-  <si>
-    <t>C5349934</t>
-  </si>
-  <si>
-    <t>Q1,Q2,Q6</t>
-  </si>
-  <si>
-    <t>SOP-8_L5.0-W4.0-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
-    <t>FDS6680A</t>
-  </si>
-  <si>
-    <t>onsemi(安森美)</t>
-  </si>
-  <si>
-    <t>C87668</t>
-  </si>
-  <si>
-    <t>场效应管(MOSFET)</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>Q3,Q4,Q7,Q8</t>
-  </si>
-  <si>
-    <t>PDFN-8_L3.1-W3.1-P0.65-LS3.4-BL</t>
-  </si>
-  <si>
-    <t>SIS412DN-T1-GE3-ES</t>
-  </si>
-  <si>
-    <t>ElecSuper(静芯)</t>
-  </si>
-  <si>
-    <t>C21713860</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>Q5</t>
-  </si>
-  <si>
-    <t>SC-70-3_L2.0-W1.3-P0.65-LS2.1-BL</t>
-  </si>
-  <si>
-    <t>BSS138W</t>
-  </si>
-  <si>
-    <t>BSS138W_C890266</t>
-  </si>
-  <si>
-    <t>C890266</t>
-  </si>
-  <si>
-    <t>Q9</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR-1</t>
-  </si>
-  <si>
-    <t>BSS84</t>
-  </si>
-  <si>
-    <t>BSS84_C7420340</t>
-  </si>
-  <si>
-    <t>C7420340</t>
-  </si>
-  <si>
-    <t>Q10</t>
-  </si>
-  <si>
-    <t>SOT-23-3_L2.9-W1.3-P1.90-LS2.4-BR</t>
-  </si>
-  <si>
-    <t>AO3401</t>
-  </si>
-  <si>
-    <t>AO3401_C5224195</t>
-  </si>
-  <si>
-    <t>C5224195</t>
-  </si>
-  <si>
-    <t>R0</t>
-  </si>
-  <si>
-    <t>R0603</t>
-  </si>
-  <si>
-    <t>2Ω</t>
-  </si>
-  <si>
-    <t>0603WAF200KT5E</t>
-  </si>
-  <si>
-    <t>UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C22977</t>
-  </si>
-  <si>
-    <t>电阻</t>
-  </si>
-  <si>
-    <t>贴片电阻</t>
-  </si>
-  <si>
-    <t>R1,R18</t>
-  </si>
-  <si>
-    <t>499kΩ</t>
-  </si>
-  <si>
-    <t>0603WAF4993T5E</t>
-  </si>
-  <si>
-    <t>C26751</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>133kΩ</t>
-  </si>
-  <si>
-    <t>0603WAF1333T5E</t>
-  </si>
-  <si>
-    <t>C22870</t>
-  </si>
-  <si>
-    <t>R3,R9,R14,R15,R20,R42</t>
-  </si>
-  <si>
-    <t>10Ω</t>
-  </si>
-  <si>
-    <t>0603WAF100JT5E</t>
-  </si>
-  <si>
-    <t>C22859</t>
-  </si>
-  <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>316kΩ</t>
-  </si>
-  <si>
-    <t>0603WAF3163T5E</t>
-  </si>
-  <si>
-    <t>C25814</t>
-  </si>
-  <si>
-    <t>R5,R44,R48</t>
-  </si>
-  <si>
-    <t>100kΩ</t>
-  </si>
-  <si>
-    <t>0603WAF1003T5E</t>
-  </si>
-  <si>
-    <t>C25803</t>
-  </si>
-  <si>
-    <t>R6,R10,R11,R55,R67</t>
-  </si>
-  <si>
-    <t>4.7kΩ</t>
-  </si>
-  <si>
-    <t>0603WAF4701T5E</t>
-  </si>
-  <si>
-    <t>C23162</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>14.3kΩ</t>
-  </si>
-  <si>
-    <t>FRC0603F1432TS</t>
-  </si>
-  <si>
     <t>C2933145</t>
   </si>
   <si>
@@ -865,34 +871,31 @@
     <t>电流采样电阻/分流器</t>
   </si>
   <si>
-    <t>R29,R30,R40,R52,R61</t>
+    <t>R29,R30,R40,R52,R61,R78</t>
   </si>
   <si>
     <t>100Ω</t>
   </si>
   <si>
-    <t>0603WAF1000T5E</t>
-  </si>
-  <si>
-    <t>C22775</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>R34,R35,R36,R37,R38,R39,R53,R54,R57,R78</t>
+    <t>0603WAF1000T5E,FRC0603F1000TS</t>
+  </si>
+  <si>
+    <t>FOJAN(富捷),UNI-ROYAL(厚声)</t>
+  </si>
+  <si>
+    <t>C22775,C2906981</t>
+  </si>
+  <si>
+    <t>R34,R35,R36,R37,R38,R39,R53,R54,R57</t>
   </si>
   <si>
     <t>1kΩ</t>
   </si>
   <si>
-    <t>0603WAF1001T5E,FRC0603F1001TS</t>
-  </si>
-  <si>
-    <t>FOJAN(富捷),UNI-ROYAL(厚声)</t>
-  </si>
-  <si>
-    <t>C21190,C2907002</t>
+    <t>0603WAF1001T5E</t>
+  </si>
+  <si>
+    <t>C21190</t>
   </si>
   <si>
     <t>R43,R47</t>
@@ -1171,7 +1174,7 @@
     <t>49</t>
   </si>
   <si>
-    <t>U?</t>
+    <t>U9</t>
   </si>
   <si>
     <t>DFN-4_L2.0-W2.0-P1.00-BL-EP</t>
@@ -1868,34 +1871,34 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>49</v>
-      </c>
-      <c r="B7" t="s">
-        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
         <v>51</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
         <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>54</v>
       </c>
       <c r="K7" t="s">
         <v>31</v>
@@ -1907,7 +1910,7 @@
         <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1915,31 +1918,31 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" t="s">
         <v>57</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>31</v>
@@ -1951,7 +1954,7 @@
         <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1959,31 +1962,31 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
         <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
         <v>61</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
       <c r="K9" t="s">
         <v>31</v>
@@ -1995,7 +1998,7 @@
         <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2003,31 +2006,31 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
         <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
         <v>65</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>66</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
@@ -2039,7 +2042,7 @@
         <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2047,31 +2050,31 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
         <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
         <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>31</v>
@@ -2083,7 +2086,7 @@
         <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2091,31 +2094,31 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
         <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
       </c>
       <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
         <v>73</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>74</v>
       </c>
       <c r="K12" t="s">
         <v>31</v>
@@ -2127,7 +2130,7 @@
         <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2135,31 +2138,31 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
         <v>76</v>
-      </c>
-      <c r="E13" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" t="s">
-        <v>77</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" t="s">
         <v>77</v>
-      </c>
-      <c r="I13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J13" t="s">
-        <v>78</v>
       </c>
       <c r="K13" t="s">
         <v>31</v>
@@ -2171,7 +2174,7 @@
         <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2179,43 +2182,43 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
         <v>79</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>80</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>81</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
+        <v>81</v>
+      </c>
+      <c r="G14" t="s">
         <v>82</v>
       </c>
-      <c r="F14" t="s">
-        <v>82</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="H14" t="s">
+        <v>81</v>
+      </c>
+      <c r="I14" t="s">
+        <v>20</v>
+      </c>
+      <c r="J14" t="s">
         <v>83</v>
       </c>
-      <c r="H14" t="s">
-        <v>82</v>
-      </c>
-      <c r="I14" t="s">
-        <v>20</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>84</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" t="s">
         <v>85</v>
       </c>
-      <c r="L14" t="s">
+      <c r="M14" t="s">
         <v>86</v>
       </c>
-      <c r="M14" t="s">
-        <v>49</v>
-      </c>
       <c r="N14" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2229,7 +2232,7 @@
         <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
         <v>89</v>
@@ -2238,7 +2241,7 @@
         <v>89</v>
       </c>
       <c r="G15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H15" t="s">
         <v>89</v>
@@ -2250,10 +2253,10 @@
         <v>90</v>
       </c>
       <c r="K15" t="s">
+        <v>84</v>
+      </c>
+      <c r="L15" t="s">
         <v>85</v>
-      </c>
-      <c r="L15" t="s">
-        <v>86</v>
       </c>
       <c r="M15" t="s">
         <v>24</v>
@@ -2273,7 +2276,7 @@
         <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
         <v>93</v>
@@ -2317,34 +2320,34 @@
         <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>101</v>
       </c>
       <c r="F17" t="s">
+        <v>101</v>
+      </c>
+      <c r="G17" t="s">
         <v>102</v>
       </c>
-      <c r="G17" t="s">
+      <c r="H17" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" t="s">
         <v>103</v>
       </c>
-      <c r="H17" t="s">
-        <v>102</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" t="s">
-        <v>104</v>
-      </c>
       <c r="K17" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="L17" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="N17" t="s">
         <v>101</v>
@@ -2355,43 +2358,43 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" t="s">
         <v>106</v>
       </c>
-      <c r="C18" t="s">
+      <c r="E18" t="s">
+        <v>106</v>
+      </c>
+      <c r="F18" t="s">
         <v>107</v>
       </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
+      <c r="G18" t="s">
         <v>108</v>
       </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" t="s">
+        <v>20</v>
+      </c>
+      <c r="J18" t="s">
         <v>109</v>
       </c>
-      <c r="G18" t="s">
+      <c r="K18" t="s">
+        <v>31</v>
+      </c>
+      <c r="L18" t="s">
         <v>110</v>
       </c>
-      <c r="H18" t="s">
-        <v>108</v>
-      </c>
-      <c r="I18" t="s">
-        <v>20</v>
-      </c>
-      <c r="J18" t="s">
-        <v>111</v>
-      </c>
-      <c r="K18" t="s">
-        <v>112</v>
-      </c>
-      <c r="L18" t="s">
-        <v>113</v>
-      </c>
       <c r="M18" t="s">
         <v>24</v>
       </c>
       <c r="N18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2399,92 +2402,92 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" t="s">
+        <v>112</v>
+      </c>
+      <c r="D19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19" t="s">
+        <v>113</v>
+      </c>
+      <c r="F19" t="s">
         <v>114</v>
       </c>
-      <c r="C19" t="s">
+      <c r="G19" t="s">
         <v>115</v>
       </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
+      <c r="H19" t="s">
+        <v>113</v>
+      </c>
+      <c r="I19" t="s">
+        <v>20</v>
+      </c>
+      <c r="J19" t="s">
         <v>116</v>
       </c>
-      <c r="F19" t="s">
-        <v>116</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="K19" t="s">
         <v>117</v>
       </c>
-      <c r="H19" t="s">
-        <v>116</v>
-      </c>
-      <c r="I19" t="s">
-        <v>20</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="L19" t="s">
         <v>118</v>
       </c>
-      <c r="K19" t="s">
-        <v>119</v>
-      </c>
-      <c r="L19" t="s">
-        <v>120</v>
-      </c>
       <c r="M19" t="s">
-        <v>121</v>
+        <v>24</v>
       </c>
       <c r="N19" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B20" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" t="s">
+        <v>120</v>
+      </c>
+      <c r="D20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G20" t="s">
         <v>122</v>
       </c>
-      <c r="C20" t="s">
+      <c r="H20" t="s">
+        <v>121</v>
+      </c>
+      <c r="I20" t="s">
+        <v>20</v>
+      </c>
+      <c r="J20" t="s">
         <v>123</v>
       </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="K20" t="s">
         <v>124</v>
       </c>
-      <c r="F20" t="s">
+      <c r="L20" t="s">
         <v>125</v>
       </c>
-      <c r="G20" t="s">
-        <v>110</v>
-      </c>
-      <c r="H20" t="s">
-        <v>124</v>
-      </c>
-      <c r="I20" t="s">
-        <v>20</v>
-      </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>126</v>
       </c>
-      <c r="K20" t="s">
-        <v>119</v>
-      </c>
-      <c r="L20" t="s">
-        <v>120</v>
-      </c>
-      <c r="M20" t="s">
-        <v>24</v>
-      </c>
       <c r="N20" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>127</v>
@@ -2493,16 +2496,16 @@
         <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
       </c>
       <c r="F21" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G21" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="H21" t="s">
         <v>129</v>
@@ -2514,13 +2517,13 @@
         <v>131</v>
       </c>
       <c r="K21" t="s">
-        <v>85</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="M21" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="N21" t="s">
         <v>129</v>
@@ -2531,25 +2534,25 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
         <v>133</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
         <v>134</v>
       </c>
-      <c r="D22" t="s">
-        <v>81</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
+        <v>134</v>
+      </c>
+      <c r="G22" t="s">
         <v>135</v>
       </c>
-      <c r="F22" t="s">
-        <v>135</v>
-      </c>
-      <c r="G22" t="s">
-        <v>94</v>
-      </c>
       <c r="H22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I22" t="s">
         <v>20</v>
@@ -2558,16 +2561,16 @@
         <v>136</v>
       </c>
       <c r="K22" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="L22" t="s">
         <v>137</v>
       </c>
       <c r="M22" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2581,7 +2584,7 @@
         <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" t="s">
         <v>140</v>
@@ -2590,7 +2593,7 @@
         <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="H23" t="s">
         <v>140</v>
@@ -2599,13 +2602,13 @@
         <v>20</v>
       </c>
       <c r="J23" t="s">
+        <v>141</v>
+      </c>
+      <c r="K23" t="s">
+        <v>96</v>
+      </c>
+      <c r="L23" t="s">
         <v>142</v>
-      </c>
-      <c r="K23" t="s">
-        <v>85</v>
-      </c>
-      <c r="L23" t="s">
-        <v>143</v>
       </c>
       <c r="M23" t="s">
         <v>98</v>
@@ -2619,25 +2622,25 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" t="s">
         <v>144</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>80</v>
+      </c>
+      <c r="E24" t="s">
         <v>145</v>
       </c>
-      <c r="D24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
+        <v>145</v>
+      </c>
+      <c r="G24" t="s">
         <v>146</v>
       </c>
-      <c r="F24" t="s">
-        <v>146</v>
-      </c>
-      <c r="G24" t="s">
-        <v>141</v>
-      </c>
       <c r="H24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="I24" t="s">
         <v>20</v>
@@ -2646,16 +2649,16 @@
         <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L24" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="M24" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="N24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2663,43 +2666,43 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C25" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E25" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" t="s">
+        <v>152</v>
+      </c>
+      <c r="I25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J25" t="s">
+        <v>154</v>
+      </c>
+      <c r="K25" t="s">
+        <v>155</v>
+      </c>
+      <c r="L25" t="s">
+        <v>156</v>
+      </c>
+      <c r="M25" t="s">
+        <v>24</v>
+      </c>
+      <c r="N25" t="s">
         <v>151</v>
-      </c>
-      <c r="G25" t="s">
-        <v>152</v>
-      </c>
-      <c r="H25" t="s">
-        <v>151</v>
-      </c>
-      <c r="I25" t="s">
-        <v>20</v>
-      </c>
-      <c r="J25" t="s">
-        <v>153</v>
-      </c>
-      <c r="K25" t="s">
-        <v>154</v>
-      </c>
-      <c r="L25" t="s">
-        <v>155</v>
-      </c>
-      <c r="M25" t="s">
-        <v>24</v>
-      </c>
-      <c r="N25" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2707,43 +2710,43 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C26" t="s">
+        <v>158</v>
+      </c>
+      <c r="D26" t="s">
+        <v>159</v>
+      </c>
+      <c r="E26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F26" t="s">
+        <v>160</v>
+      </c>
+      <c r="G26" t="s">
+        <v>153</v>
+      </c>
+      <c r="H26" t="s">
+        <v>160</v>
+      </c>
+      <c r="I26" t="s">
+        <v>20</v>
+      </c>
+      <c r="J26" t="s">
+        <v>161</v>
+      </c>
+      <c r="K26" t="s">
+        <v>155</v>
+      </c>
+      <c r="L26" t="s">
         <v>156</v>
       </c>
-      <c r="C26" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" t="s">
-        <v>158</v>
-      </c>
-      <c r="E26" t="s">
-        <v>158</v>
-      </c>
-      <c r="F26" t="s">
+      <c r="M26" t="s">
+        <v>24</v>
+      </c>
+      <c r="N26" t="s">
         <v>159</v>
-      </c>
-      <c r="G26" t="s">
-        <v>152</v>
-      </c>
-      <c r="H26" t="s">
-        <v>159</v>
-      </c>
-      <c r="I26" t="s">
-        <v>20</v>
-      </c>
-      <c r="J26" t="s">
-        <v>160</v>
-      </c>
-      <c r="K26" t="s">
-        <v>154</v>
-      </c>
-      <c r="L26" t="s">
-        <v>155</v>
-      </c>
-      <c r="M26" t="s">
-        <v>24</v>
-      </c>
-      <c r="N26" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2751,43 +2754,43 @@
         <v>14</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C27" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G27" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" t="s">
         <v>164</v>
       </c>
-      <c r="H27" t="s">
-        <v>163</v>
-      </c>
       <c r="I27" t="s">
         <v>20</v>
       </c>
       <c r="J27" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K27" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L27" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M27" t="s">
         <v>24</v>
       </c>
       <c r="N27" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2795,43 +2798,43 @@
         <v>14</v>
       </c>
       <c r="B28" t="s">
+        <v>169</v>
+      </c>
+      <c r="C28" t="s">
+        <v>170</v>
+      </c>
+      <c r="D28" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" t="s">
+        <v>171</v>
+      </c>
+      <c r="F28" t="s">
+        <v>171</v>
+      </c>
+      <c r="G28" t="s">
+        <v>165</v>
+      </c>
+      <c r="H28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I28" t="s">
+        <v>20</v>
+      </c>
+      <c r="J28" t="s">
+        <v>172</v>
+      </c>
+      <c r="K28" t="s">
+        <v>167</v>
+      </c>
+      <c r="L28" t="s">
         <v>168</v>
       </c>
-      <c r="C28" t="s">
-        <v>169</v>
-      </c>
-      <c r="D28" t="s">
-        <v>81</v>
-      </c>
-      <c r="E28" t="s">
-        <v>170</v>
-      </c>
-      <c r="F28" t="s">
-        <v>170</v>
-      </c>
-      <c r="G28" t="s">
-        <v>164</v>
-      </c>
-      <c r="H28" t="s">
-        <v>170</v>
-      </c>
-      <c r="I28" t="s">
-        <v>20</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
+        <v>24</v>
+      </c>
+      <c r="N28" t="s">
         <v>171</v>
-      </c>
-      <c r="K28" t="s">
-        <v>166</v>
-      </c>
-      <c r="L28" t="s">
-        <v>167</v>
-      </c>
-      <c r="M28" t="s">
-        <v>24</v>
-      </c>
-      <c r="N28" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2839,43 +2842,43 @@
         <v>14</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G29" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I29" t="s">
         <v>20</v>
       </c>
       <c r="J29" t="s">
+        <v>176</v>
+      </c>
+      <c r="K29" t="s">
+        <v>167</v>
+      </c>
+      <c r="L29" t="s">
+        <v>168</v>
+      </c>
+      <c r="M29" t="s">
+        <v>24</v>
+      </c>
+      <c r="N29" t="s">
         <v>175</v>
-      </c>
-      <c r="K29" t="s">
-        <v>166</v>
-      </c>
-      <c r="L29" t="s">
-        <v>167</v>
-      </c>
-      <c r="M29" t="s">
-        <v>24</v>
-      </c>
-      <c r="N29" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2883,87 +2886,87 @@
         <v>14</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G30" t="s">
+        <v>180</v>
+      </c>
+      <c r="H30" t="s">
         <v>179</v>
       </c>
-      <c r="H30" t="s">
-        <v>178</v>
-      </c>
       <c r="I30" t="s">
         <v>20</v>
       </c>
       <c r="J30" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K30" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M30" t="s">
         <v>98</v>
       </c>
       <c r="N30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B31" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C31" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G31" t="s">
+        <v>185</v>
+      </c>
+      <c r="H31" t="s">
         <v>184</v>
       </c>
-      <c r="H31" t="s">
-        <v>183</v>
-      </c>
       <c r="I31" t="s">
         <v>20</v>
       </c>
       <c r="J31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K31" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L31" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N31" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2971,43 +2974,43 @@
         <v>98</v>
       </c>
       <c r="B32" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C32" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G32" t="s">
+        <v>192</v>
+      </c>
+      <c r="H32" t="s">
         <v>191</v>
       </c>
-      <c r="H32" t="s">
-        <v>190</v>
-      </c>
       <c r="I32" t="s">
         <v>20</v>
       </c>
       <c r="J32" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K32" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L32" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M32" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N32" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -3015,43 +3018,43 @@
         <v>14</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C33" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G33" t="s">
+        <v>185</v>
+      </c>
+      <c r="H33" t="s">
         <v>197</v>
       </c>
-      <c r="G33" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" t="s">
-        <v>196</v>
-      </c>
       <c r="I33" t="s">
         <v>20</v>
       </c>
       <c r="J33" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M33" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N33" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -3059,43 +3062,43 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C34" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F34" t="s">
+        <v>203</v>
+      </c>
+      <c r="G34" t="s">
+        <v>115</v>
+      </c>
+      <c r="H34" t="s">
         <v>202</v>
       </c>
-      <c r="G34" t="s">
-        <v>110</v>
-      </c>
-      <c r="H34" t="s">
-        <v>201</v>
-      </c>
       <c r="I34" t="s">
         <v>20</v>
       </c>
       <c r="J34" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K34" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L34" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N34" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -3103,43 +3106,43 @@
         <v>14</v>
       </c>
       <c r="B35" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C35" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F35" t="s">
+        <v>208</v>
+      </c>
+      <c r="G35" t="s">
+        <v>192</v>
+      </c>
+      <c r="H35" t="s">
         <v>207</v>
       </c>
-      <c r="G35" t="s">
-        <v>191</v>
-      </c>
-      <c r="H35" t="s">
-        <v>206</v>
-      </c>
       <c r="I35" t="s">
         <v>20</v>
       </c>
       <c r="J35" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K35" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="L35" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M35" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="N35" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -3147,43 +3150,43 @@
         <v>14</v>
       </c>
       <c r="B36" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C36" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F36" t="s">
+        <v>213</v>
+      </c>
+      <c r="G36" t="s">
+        <v>214</v>
+      </c>
+      <c r="H36" t="s">
+        <v>213</v>
+      </c>
+      <c r="I36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s">
+        <v>215</v>
+      </c>
+      <c r="K36" t="s">
+        <v>216</v>
+      </c>
+      <c r="L36" t="s">
+        <v>217</v>
+      </c>
+      <c r="M36" t="s">
+        <v>24</v>
+      </c>
+      <c r="N36" t="s">
         <v>212</v>
-      </c>
-      <c r="G36" t="s">
-        <v>213</v>
-      </c>
-      <c r="H36" t="s">
-        <v>212</v>
-      </c>
-      <c r="I36" t="s">
-        <v>20</v>
-      </c>
-      <c r="J36" t="s">
-        <v>214</v>
-      </c>
-      <c r="K36" t="s">
-        <v>215</v>
-      </c>
-      <c r="L36" t="s">
-        <v>216</v>
-      </c>
-      <c r="M36" t="s">
-        <v>24</v>
-      </c>
-      <c r="N36" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -3191,43 +3194,43 @@
         <v>24</v>
       </c>
       <c r="B37" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" t="s">
+        <v>211</v>
+      </c>
+      <c r="D37" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" t="s">
+        <v>219</v>
+      </c>
+      <c r="F37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G37" t="s">
+        <v>214</v>
+      </c>
+      <c r="H37" t="s">
+        <v>220</v>
+      </c>
+      <c r="I37" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s">
+        <v>221</v>
+      </c>
+      <c r="K37" t="s">
+        <v>216</v>
+      </c>
+      <c r="L37" t="s">
         <v>217</v>
       </c>
-      <c r="C37" t="s">
-        <v>210</v>
-      </c>
-      <c r="D37" t="s">
-        <v>218</v>
-      </c>
-      <c r="E37" t="s">
-        <v>218</v>
-      </c>
-      <c r="F37" t="s">
+      <c r="M37" t="s">
+        <v>24</v>
+      </c>
+      <c r="N37" t="s">
         <v>219</v>
-      </c>
-      <c r="G37" t="s">
-        <v>213</v>
-      </c>
-      <c r="H37" t="s">
-        <v>219</v>
-      </c>
-      <c r="I37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J37" t="s">
-        <v>220</v>
-      </c>
-      <c r="K37" t="s">
-        <v>215</v>
-      </c>
-      <c r="L37" t="s">
-        <v>216</v>
-      </c>
-      <c r="M37" t="s">
-        <v>24</v>
-      </c>
-      <c r="N37" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
@@ -3235,87 +3238,87 @@
         <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E38" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F38" t="s">
+        <v>224</v>
+      </c>
+      <c r="G38" t="s">
+        <v>214</v>
+      </c>
+      <c r="H38" t="s">
+        <v>224</v>
+      </c>
+      <c r="I38" t="s">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s">
+        <v>225</v>
+      </c>
+      <c r="K38" t="s">
+        <v>216</v>
+      </c>
+      <c r="L38" t="s">
+        <v>217</v>
+      </c>
+      <c r="M38" t="s">
+        <v>24</v>
+      </c>
+      <c r="N38" t="s">
         <v>223</v>
-      </c>
-      <c r="G38" t="s">
-        <v>213</v>
-      </c>
-      <c r="H38" t="s">
-        <v>223</v>
-      </c>
-      <c r="I38" t="s">
-        <v>20</v>
-      </c>
-      <c r="J38" t="s">
-        <v>224</v>
-      </c>
-      <c r="K38" t="s">
-        <v>215</v>
-      </c>
-      <c r="L38" t="s">
-        <v>216</v>
-      </c>
-      <c r="M38" t="s">
-        <v>24</v>
-      </c>
-      <c r="N38" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="B39" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C39" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E39" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F39" t="s">
+        <v>228</v>
+      </c>
+      <c r="G39" t="s">
+        <v>214</v>
+      </c>
+      <c r="H39" t="s">
+        <v>228</v>
+      </c>
+      <c r="I39" t="s">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s">
+        <v>229</v>
+      </c>
+      <c r="K39" t="s">
+        <v>216</v>
+      </c>
+      <c r="L39" t="s">
+        <v>217</v>
+      </c>
+      <c r="M39" t="s">
+        <v>24</v>
+      </c>
+      <c r="N39" t="s">
         <v>227</v>
-      </c>
-      <c r="G39" t="s">
-        <v>213</v>
-      </c>
-      <c r="H39" t="s">
-        <v>227</v>
-      </c>
-      <c r="I39" t="s">
-        <v>20</v>
-      </c>
-      <c r="J39" t="s">
-        <v>228</v>
-      </c>
-      <c r="K39" t="s">
-        <v>215</v>
-      </c>
-      <c r="L39" t="s">
-        <v>216</v>
-      </c>
-      <c r="M39" t="s">
-        <v>24</v>
-      </c>
-      <c r="N39" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
@@ -3323,87 +3326,87 @@
         <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="E40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F40" t="s">
+        <v>232</v>
+      </c>
+      <c r="G40" t="s">
+        <v>214</v>
+      </c>
+      <c r="H40" t="s">
+        <v>232</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
+        <v>233</v>
+      </c>
+      <c r="K40" t="s">
+        <v>216</v>
+      </c>
+      <c r="L40" t="s">
+        <v>217</v>
+      </c>
+      <c r="M40" t="s">
+        <v>24</v>
+      </c>
+      <c r="N40" t="s">
         <v>231</v>
-      </c>
-      <c r="G40" t="s">
-        <v>213</v>
-      </c>
-      <c r="H40" t="s">
-        <v>231</v>
-      </c>
-      <c r="I40" t="s">
-        <v>20</v>
-      </c>
-      <c r="J40" t="s">
-        <v>232</v>
-      </c>
-      <c r="K40" t="s">
-        <v>215</v>
-      </c>
-      <c r="L40" t="s">
-        <v>216</v>
-      </c>
-      <c r="M40" t="s">
-        <v>24</v>
-      </c>
-      <c r="N40" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C41" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="E41" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F41" t="s">
+        <v>236</v>
+      </c>
+      <c r="G41" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" t="s">
+        <v>236</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s">
+        <v>237</v>
+      </c>
+      <c r="K41" t="s">
+        <v>216</v>
+      </c>
+      <c r="L41" t="s">
+        <v>217</v>
+      </c>
+      <c r="M41" t="s">
+        <v>24</v>
+      </c>
+      <c r="N41" t="s">
         <v>235</v>
-      </c>
-      <c r="G41" t="s">
-        <v>213</v>
-      </c>
-      <c r="H41" t="s">
-        <v>235</v>
-      </c>
-      <c r="I41" t="s">
-        <v>20</v>
-      </c>
-      <c r="J41" t="s">
-        <v>236</v>
-      </c>
-      <c r="K41" t="s">
-        <v>215</v>
-      </c>
-      <c r="L41" t="s">
-        <v>216</v>
-      </c>
-      <c r="M41" t="s">
-        <v>24</v>
-      </c>
-      <c r="N41" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
@@ -3411,43 +3414,43 @@
         <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C42" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E42" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F42" t="s">
+        <v>240</v>
+      </c>
+      <c r="G42" t="s">
+        <v>214</v>
+      </c>
+      <c r="H42" t="s">
+        <v>240</v>
+      </c>
+      <c r="I42" t="s">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s">
+        <v>241</v>
+      </c>
+      <c r="K42" t="s">
+        <v>216</v>
+      </c>
+      <c r="L42" t="s">
+        <v>217</v>
+      </c>
+      <c r="M42" t="s">
+        <v>24</v>
+      </c>
+      <c r="N42" t="s">
         <v>239</v>
-      </c>
-      <c r="G42" t="s">
-        <v>213</v>
-      </c>
-      <c r="H42" t="s">
-        <v>239</v>
-      </c>
-      <c r="I42" t="s">
-        <v>20</v>
-      </c>
-      <c r="J42" t="s">
-        <v>240</v>
-      </c>
-      <c r="K42" t="s">
-        <v>215</v>
-      </c>
-      <c r="L42" t="s">
-        <v>216</v>
-      </c>
-      <c r="M42" t="s">
-        <v>24</v>
-      </c>
-      <c r="N42" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
@@ -3455,43 +3458,43 @@
         <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C43" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E43" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F43" t="s">
+        <v>244</v>
+      </c>
+      <c r="G43" t="s">
+        <v>245</v>
+      </c>
+      <c r="H43" t="s">
+        <v>244</v>
+      </c>
+      <c r="I43" t="s">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s">
+        <v>246</v>
+      </c>
+      <c r="K43" t="s">
+        <v>216</v>
+      </c>
+      <c r="L43" t="s">
+        <v>217</v>
+      </c>
+      <c r="M43" t="s">
+        <v>24</v>
+      </c>
+      <c r="N43" t="s">
         <v>243</v>
-      </c>
-      <c r="G43" t="s">
-        <v>37</v>
-      </c>
-      <c r="H43" t="s">
-        <v>243</v>
-      </c>
-      <c r="I43" t="s">
-        <v>20</v>
-      </c>
-      <c r="J43" t="s">
-        <v>244</v>
-      </c>
-      <c r="K43" t="s">
-        <v>215</v>
-      </c>
-      <c r="L43" t="s">
-        <v>216</v>
-      </c>
-      <c r="M43" t="s">
-        <v>24</v>
-      </c>
-      <c r="N43" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
@@ -3499,43 +3502,43 @@
         <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E44" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F44" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G44" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H44" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="I44" t="s">
         <v>20</v>
       </c>
       <c r="J44" t="s">
+        <v>250</v>
+      </c>
+      <c r="K44" t="s">
+        <v>216</v>
+      </c>
+      <c r="L44" t="s">
+        <v>217</v>
+      </c>
+      <c r="M44" t="s">
+        <v>24</v>
+      </c>
+      <c r="N44" t="s">
         <v>248</v>
-      </c>
-      <c r="K44" t="s">
-        <v>215</v>
-      </c>
-      <c r="L44" t="s">
-        <v>216</v>
-      </c>
-      <c r="M44" t="s">
-        <v>24</v>
-      </c>
-      <c r="N44" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
@@ -3543,87 +3546,87 @@
         <v>39</v>
       </c>
       <c r="B45" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C45" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E45" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G45" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H45" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
       <c r="J45" t="s">
+        <v>254</v>
+      </c>
+      <c r="K45" t="s">
+        <v>216</v>
+      </c>
+      <c r="L45" t="s">
+        <v>217</v>
+      </c>
+      <c r="M45" t="s">
+        <v>24</v>
+      </c>
+      <c r="N45" t="s">
         <v>252</v>
-      </c>
-      <c r="K45" t="s">
-        <v>215</v>
-      </c>
-      <c r="L45" t="s">
-        <v>216</v>
-      </c>
-      <c r="M45" t="s">
-        <v>24</v>
-      </c>
-      <c r="N45" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C46" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E46" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G46" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="H46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
       <c r="J46" t="s">
+        <v>259</v>
+      </c>
+      <c r="K46" t="s">
+        <v>216</v>
+      </c>
+      <c r="L46" t="s">
+        <v>217</v>
+      </c>
+      <c r="M46" t="s">
+        <v>24</v>
+      </c>
+      <c r="N46" t="s">
         <v>257</v>
-      </c>
-      <c r="K46" t="s">
-        <v>215</v>
-      </c>
-      <c r="L46" t="s">
-        <v>216</v>
-      </c>
-      <c r="M46" t="s">
-        <v>24</v>
-      </c>
-      <c r="N46" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
@@ -3631,43 +3634,43 @@
         <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C47" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E47" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="G47" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="H47" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
       <c r="J47" t="s">
+        <v>263</v>
+      </c>
+      <c r="K47" t="s">
+        <v>216</v>
+      </c>
+      <c r="L47" t="s">
+        <v>217</v>
+      </c>
+      <c r="M47" t="s">
+        <v>24</v>
+      </c>
+      <c r="N47" t="s">
         <v>261</v>
-      </c>
-      <c r="K47" t="s">
-        <v>215</v>
-      </c>
-      <c r="L47" t="s">
-        <v>216</v>
-      </c>
-      <c r="M47" t="s">
-        <v>24</v>
-      </c>
-      <c r="N47" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -3675,43 +3678,43 @@
         <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C48" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="H48" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
       <c r="J48" t="s">
+        <v>267</v>
+      </c>
+      <c r="K48" t="s">
+        <v>216</v>
+      </c>
+      <c r="L48" t="s">
+        <v>217</v>
+      </c>
+      <c r="M48" t="s">
+        <v>24</v>
+      </c>
+      <c r="N48" t="s">
         <v>265</v>
-      </c>
-      <c r="K48" t="s">
-        <v>215</v>
-      </c>
-      <c r="L48" t="s">
-        <v>216</v>
-      </c>
-      <c r="M48" t="s">
-        <v>24</v>
-      </c>
-      <c r="N48" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -3719,43 +3722,43 @@
         <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C49" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E49" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="F49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="G49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H49" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
       <c r="J49" t="s">
+        <v>271</v>
+      </c>
+      <c r="K49" t="s">
+        <v>216</v>
+      </c>
+      <c r="L49" t="s">
+        <v>217</v>
+      </c>
+      <c r="M49" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" t="s">
         <v>269</v>
-      </c>
-      <c r="K49" t="s">
-        <v>215</v>
-      </c>
-      <c r="L49" t="s">
-        <v>216</v>
-      </c>
-      <c r="M49" t="s">
-        <v>24</v>
-      </c>
-      <c r="N49" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -3763,43 +3766,43 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C50" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E50" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="G50" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="I50" t="s">
         <v>20</v>
       </c>
       <c r="J50" t="s">
+        <v>275</v>
+      </c>
+      <c r="K50" t="s">
+        <v>216</v>
+      </c>
+      <c r="L50" t="s">
+        <v>217</v>
+      </c>
+      <c r="M50" t="s">
+        <v>24</v>
+      </c>
+      <c r="N50" t="s">
         <v>273</v>
-      </c>
-      <c r="K50" t="s">
-        <v>215</v>
-      </c>
-      <c r="L50" t="s">
-        <v>216</v>
-      </c>
-      <c r="M50" t="s">
-        <v>24</v>
-      </c>
-      <c r="N50" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -3807,43 +3810,43 @@
         <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C51" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E51" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="G51" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I51" t="s">
         <v>20</v>
       </c>
       <c r="J51" t="s">
+        <v>279</v>
+      </c>
+      <c r="K51" t="s">
+        <v>216</v>
+      </c>
+      <c r="L51" t="s">
+        <v>217</v>
+      </c>
+      <c r="M51" t="s">
+        <v>24</v>
+      </c>
+      <c r="N51" t="s">
         <v>277</v>
-      </c>
-      <c r="K51" t="s">
-        <v>215</v>
-      </c>
-      <c r="L51" t="s">
-        <v>216</v>
-      </c>
-      <c r="M51" t="s">
-        <v>24</v>
-      </c>
-      <c r="N51" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -3851,131 +3854,131 @@
         <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="C52" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E52" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G52" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H52" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
       </c>
       <c r="J52" t="s">
+        <v>284</v>
+      </c>
+      <c r="K52" t="s">
+        <v>216</v>
+      </c>
+      <c r="L52" t="s">
+        <v>285</v>
+      </c>
+      <c r="M52" t="s">
+        <v>24</v>
+      </c>
+      <c r="N52" t="s">
         <v>282</v>
-      </c>
-      <c r="K52" t="s">
-        <v>215</v>
-      </c>
-      <c r="L52" t="s">
-        <v>283</v>
-      </c>
-      <c r="M52" t="s">
-        <v>24</v>
-      </c>
-      <c r="N52" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E53" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F53" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="G53" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="H53" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
       </c>
       <c r="J53" t="s">
+        <v>290</v>
+      </c>
+      <c r="K53" t="s">
+        <v>216</v>
+      </c>
+      <c r="L53" t="s">
+        <v>217</v>
+      </c>
+      <c r="M53" t="s">
+        <v>24</v>
+      </c>
+      <c r="N53" t="s">
         <v>287</v>
-      </c>
-      <c r="K53" t="s">
-        <v>215</v>
-      </c>
-      <c r="L53" t="s">
-        <v>216</v>
-      </c>
-      <c r="M53" t="s">
-        <v>24</v>
-      </c>
-      <c r="N53" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>288</v>
+        <v>194</v>
       </c>
       <c r="B54" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C54" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D54" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E54" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F54" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="G54" t="s">
+        <v>214</v>
+      </c>
+      <c r="H54" t="s">
+        <v>293</v>
+      </c>
+      <c r="I54" t="s">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s">
+        <v>294</v>
+      </c>
+      <c r="K54" t="s">
+        <v>216</v>
+      </c>
+      <c r="L54" t="s">
+        <v>217</v>
+      </c>
+      <c r="M54" t="s">
+        <v>24</v>
+      </c>
+      <c r="N54" t="s">
         <v>292</v>
-      </c>
-      <c r="H54" t="s">
-        <v>291</v>
-      </c>
-      <c r="I54" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" t="s">
-        <v>293</v>
-      </c>
-      <c r="K54" t="s">
-        <v>215</v>
-      </c>
-      <c r="L54" t="s">
-        <v>216</v>
-      </c>
-      <c r="M54" t="s">
-        <v>24</v>
-      </c>
-      <c r="N54" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3983,43 +3986,43 @@
         <v>24</v>
       </c>
       <c r="B55" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F55" t="s">
+        <v>297</v>
+      </c>
+      <c r="G55" t="s">
+        <v>245</v>
+      </c>
+      <c r="H55" t="s">
+        <v>297</v>
+      </c>
+      <c r="I55" t="s">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s">
+        <v>298</v>
+      </c>
+      <c r="K55" t="s">
+        <v>216</v>
+      </c>
+      <c r="L55" t="s">
+        <v>217</v>
+      </c>
+      <c r="M55" t="s">
+        <v>24</v>
+      </c>
+      <c r="N55" t="s">
         <v>296</v>
-      </c>
-      <c r="G55" t="s">
-        <v>37</v>
-      </c>
-      <c r="H55" t="s">
-        <v>296</v>
-      </c>
-      <c r="I55" t="s">
-        <v>20</v>
-      </c>
-      <c r="J55" t="s">
-        <v>297</v>
-      </c>
-      <c r="K55" t="s">
-        <v>215</v>
-      </c>
-      <c r="L55" t="s">
-        <v>216</v>
-      </c>
-      <c r="M55" t="s">
-        <v>24</v>
-      </c>
-      <c r="N55" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4027,43 +4030,43 @@
         <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C56" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D56" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G56" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="H56" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
       </c>
       <c r="J56" t="s">
+        <v>301</v>
+      </c>
+      <c r="K56" t="s">
+        <v>302</v>
+      </c>
+      <c r="L56" t="s">
+        <v>303</v>
+      </c>
+      <c r="M56" t="s">
+        <v>24</v>
+      </c>
+      <c r="N56" t="s">
         <v>300</v>
-      </c>
-      <c r="K56" t="s">
-        <v>301</v>
-      </c>
-      <c r="L56" t="s">
-        <v>302</v>
-      </c>
-      <c r="M56" t="s">
-        <v>24</v>
-      </c>
-      <c r="N56" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -4071,43 +4074,43 @@
         <v>24</v>
       </c>
       <c r="B57" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C57" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D57" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E57" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F57" t="s">
+        <v>306</v>
+      </c>
+      <c r="G57" t="s">
+        <v>214</v>
+      </c>
+      <c r="H57" t="s">
+        <v>306</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s">
+        <v>307</v>
+      </c>
+      <c r="K57" t="s">
+        <v>216</v>
+      </c>
+      <c r="L57" t="s">
+        <v>217</v>
+      </c>
+      <c r="M57" t="s">
+        <v>24</v>
+      </c>
+      <c r="N57" t="s">
         <v>305</v>
-      </c>
-      <c r="G57" t="s">
-        <v>213</v>
-      </c>
-      <c r="H57" t="s">
-        <v>305</v>
-      </c>
-      <c r="I57" t="s">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s">
-        <v>306</v>
-      </c>
-      <c r="K57" t="s">
-        <v>215</v>
-      </c>
-      <c r="L57" t="s">
-        <v>216</v>
-      </c>
-      <c r="M57" t="s">
-        <v>24</v>
-      </c>
-      <c r="N57" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4115,43 +4118,43 @@
         <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C58" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E58" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F58" t="s">
+        <v>310</v>
+      </c>
+      <c r="G58" t="s">
+        <v>214</v>
+      </c>
+      <c r="H58" t="s">
+        <v>310</v>
+      </c>
+      <c r="I58" t="s">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s">
+        <v>311</v>
+      </c>
+      <c r="K58" t="s">
+        <v>216</v>
+      </c>
+      <c r="L58" t="s">
+        <v>217</v>
+      </c>
+      <c r="M58" t="s">
+        <v>24</v>
+      </c>
+      <c r="N58" t="s">
         <v>309</v>
-      </c>
-      <c r="G58" t="s">
-        <v>213</v>
-      </c>
-      <c r="H58" t="s">
-        <v>309</v>
-      </c>
-      <c r="I58" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" t="s">
-        <v>310</v>
-      </c>
-      <c r="K58" t="s">
-        <v>215</v>
-      </c>
-      <c r="L58" t="s">
-        <v>216</v>
-      </c>
-      <c r="M58" t="s">
-        <v>24</v>
-      </c>
-      <c r="N58" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4159,43 +4162,43 @@
         <v>24</v>
       </c>
       <c r="B59" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C59" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D59" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E59" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F59" t="s">
+        <v>314</v>
+      </c>
+      <c r="G59" t="s">
+        <v>245</v>
+      </c>
+      <c r="H59" t="s">
+        <v>314</v>
+      </c>
+      <c r="I59" t="s">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s">
+        <v>315</v>
+      </c>
+      <c r="K59" t="s">
+        <v>216</v>
+      </c>
+      <c r="L59" t="s">
+        <v>217</v>
+      </c>
+      <c r="M59" t="s">
+        <v>24</v>
+      </c>
+      <c r="N59" t="s">
         <v>313</v>
-      </c>
-      <c r="G59" t="s">
-        <v>37</v>
-      </c>
-      <c r="H59" t="s">
-        <v>313</v>
-      </c>
-      <c r="I59" t="s">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s">
-        <v>314</v>
-      </c>
-      <c r="K59" t="s">
-        <v>215</v>
-      </c>
-      <c r="L59" t="s">
-        <v>216</v>
-      </c>
-      <c r="M59" t="s">
-        <v>24</v>
-      </c>
-      <c r="N59" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -4203,43 +4206,43 @@
         <v>24</v>
       </c>
       <c r="B60" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C60" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D60" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E60" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F60" t="s">
+        <v>318</v>
+      </c>
+      <c r="G60" t="s">
+        <v>245</v>
+      </c>
+      <c r="H60" t="s">
+        <v>318</v>
+      </c>
+      <c r="I60" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s">
+        <v>319</v>
+      </c>
+      <c r="K60" t="s">
+        <v>216</v>
+      </c>
+      <c r="L60" t="s">
+        <v>217</v>
+      </c>
+      <c r="M60" t="s">
+        <v>24</v>
+      </c>
+      <c r="N60" t="s">
         <v>317</v>
-      </c>
-      <c r="G60" t="s">
-        <v>37</v>
-      </c>
-      <c r="H60" t="s">
-        <v>317</v>
-      </c>
-      <c r="I60" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s">
-        <v>318</v>
-      </c>
-      <c r="K60" t="s">
-        <v>215</v>
-      </c>
-      <c r="L60" t="s">
-        <v>216</v>
-      </c>
-      <c r="M60" t="s">
-        <v>24</v>
-      </c>
-      <c r="N60" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -4247,43 +4250,43 @@
         <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C61" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="G61" t="s">
-        <v>37</v>
+        <v>245</v>
       </c>
       <c r="H61" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
       </c>
       <c r="J61" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K61" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L61" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="M61" t="s">
         <v>24</v>
       </c>
       <c r="N61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -4291,43 +4294,43 @@
         <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E62" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F62" t="s">
+        <v>327</v>
+      </c>
+      <c r="G62" t="s">
+        <v>108</v>
+      </c>
+      <c r="H62" t="s">
+        <v>327</v>
+      </c>
+      <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s">
+        <v>328</v>
+      </c>
+      <c r="K62" t="s">
+        <v>216</v>
+      </c>
+      <c r="L62" t="s">
+        <v>285</v>
+      </c>
+      <c r="M62" t="s">
+        <v>24</v>
+      </c>
+      <c r="N62" t="s">
         <v>326</v>
-      </c>
-      <c r="G62" t="s">
-        <v>103</v>
-      </c>
-      <c r="H62" t="s">
-        <v>326</v>
-      </c>
-      <c r="I62" t="s">
-        <v>20</v>
-      </c>
-      <c r="J62" t="s">
-        <v>327</v>
-      </c>
-      <c r="K62" t="s">
-        <v>215</v>
-      </c>
-      <c r="L62" t="s">
-        <v>283</v>
-      </c>
-      <c r="M62" t="s">
-        <v>24</v>
-      </c>
-      <c r="N62" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -4335,43 +4338,43 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C63" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D63" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E63" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F63" t="s">
+        <v>331</v>
+      </c>
+      <c r="G63" t="s">
+        <v>108</v>
+      </c>
+      <c r="H63" t="s">
+        <v>331</v>
+      </c>
+      <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s">
+        <v>332</v>
+      </c>
+      <c r="K63" t="s">
+        <v>216</v>
+      </c>
+      <c r="L63" t="s">
+        <v>285</v>
+      </c>
+      <c r="M63" t="s">
+        <v>24</v>
+      </c>
+      <c r="N63" t="s">
         <v>330</v>
-      </c>
-      <c r="G63" t="s">
-        <v>103</v>
-      </c>
-      <c r="H63" t="s">
-        <v>330</v>
-      </c>
-      <c r="I63" t="s">
-        <v>20</v>
-      </c>
-      <c r="J63" t="s">
-        <v>331</v>
-      </c>
-      <c r="K63" t="s">
-        <v>215</v>
-      </c>
-      <c r="L63" t="s">
-        <v>283</v>
-      </c>
-      <c r="M63" t="s">
-        <v>24</v>
-      </c>
-      <c r="N63" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
@@ -4379,43 +4382,43 @@
         <v>98</v>
       </c>
       <c r="B64" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C64" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D64" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G64" t="s">
+        <v>336</v>
+      </c>
+      <c r="H64" t="s">
         <v>335</v>
       </c>
-      <c r="H64" t="s">
-        <v>334</v>
-      </c>
       <c r="I64" t="s">
         <v>20</v>
       </c>
       <c r="J64" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K64" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L64" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="M64" t="s">
         <v>98</v>
       </c>
       <c r="N64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
@@ -4423,43 +4426,43 @@
         <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C65" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E65" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F65" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="G65" t="s">
+        <v>343</v>
+      </c>
+      <c r="H65" t="s">
         <v>342</v>
       </c>
-      <c r="H65" t="s">
-        <v>341</v>
-      </c>
       <c r="I65" t="s">
         <v>20</v>
       </c>
       <c r="J65" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M65" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N65" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
@@ -4467,43 +4470,43 @@
         <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C66" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="G66" t="s">
+        <v>349</v>
+      </c>
+      <c r="H66" t="s">
         <v>348</v>
       </c>
-      <c r="H66" t="s">
-        <v>347</v>
-      </c>
       <c r="I66" t="s">
         <v>20</v>
       </c>
       <c r="J66" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M66" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N66" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
@@ -4511,43 +4514,43 @@
         <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C67" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D67" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F67" t="s">
+        <v>356</v>
+      </c>
+      <c r="G67" t="s">
+        <v>357</v>
+      </c>
+      <c r="H67" t="s">
         <v>355</v>
       </c>
-      <c r="G67" t="s">
-        <v>356</v>
-      </c>
-      <c r="H67" t="s">
-        <v>354</v>
-      </c>
       <c r="I67" t="s">
         <v>20</v>
       </c>
       <c r="J67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K67" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M67" t="s">
         <v>98</v>
       </c>
       <c r="N67" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
@@ -4555,43 +4558,43 @@
         <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G68" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
       </c>
       <c r="J68" t="s">
+        <v>363</v>
+      </c>
+      <c r="K68" t="s">
+        <v>351</v>
+      </c>
+      <c r="L68" t="s">
+        <v>364</v>
+      </c>
+      <c r="M68" t="s">
+        <v>365</v>
+      </c>
+      <c r="N68" t="s">
         <v>362</v>
-      </c>
-      <c r="K68" t="s">
-        <v>350</v>
-      </c>
-      <c r="L68" t="s">
-        <v>363</v>
-      </c>
-      <c r="M68" t="s">
-        <v>364</v>
-      </c>
-      <c r="N68" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
@@ -4599,43 +4602,43 @@
         <v>24</v>
       </c>
       <c r="B69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C69" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G69" t="s">
+        <v>369</v>
+      </c>
+      <c r="H69" t="s">
         <v>368</v>
       </c>
-      <c r="H69" t="s">
-        <v>367</v>
-      </c>
       <c r="I69" t="s">
         <v>20</v>
       </c>
       <c r="J69" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="K69" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L69" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M69" t="s">
         <v>98</v>
       </c>
       <c r="N69" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
@@ -4643,43 +4646,43 @@
         <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C70" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D70" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G70" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H70" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
         <v>20</v>
       </c>
       <c r="J70" t="s">
+        <v>376</v>
+      </c>
+      <c r="K70" t="s">
+        <v>377</v>
+      </c>
+      <c r="L70" t="s">
+        <v>378</v>
+      </c>
+      <c r="M70" t="s">
+        <v>188</v>
+      </c>
+      <c r="N70" t="s">
         <v>375</v>
-      </c>
-      <c r="K70" t="s">
-        <v>376</v>
-      </c>
-      <c r="L70" t="s">
-        <v>377</v>
-      </c>
-      <c r="M70" t="s">
-        <v>187</v>
-      </c>
-      <c r="N70" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
@@ -4687,43 +4690,43 @@
         <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C71" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D71" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G71" t="s">
+        <v>382</v>
+      </c>
+      <c r="H71" t="s">
         <v>381</v>
       </c>
-      <c r="H71" t="s">
-        <v>380</v>
-      </c>
       <c r="I71" t="s">
         <v>20</v>
       </c>
       <c r="J71" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K71" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L71" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M71" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N71" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
@@ -4731,43 +4734,43 @@
         <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="G72" t="s">
+        <v>390</v>
+      </c>
+      <c r="H72" t="s">
         <v>389</v>
       </c>
-      <c r="H72" t="s">
-        <v>388</v>
-      </c>
       <c r="I72" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="J72" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K72" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="L72" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M72" t="s">
         <v>39</v>
       </c>
       <c r="N72" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
@@ -4775,43 +4778,43 @@
         <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C73" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E73" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F73" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G73" t="s">
+        <v>397</v>
+      </c>
+      <c r="H73" t="s">
         <v>396</v>
       </c>
-      <c r="H73" t="s">
-        <v>395</v>
-      </c>
       <c r="I73" t="s">
         <v>20</v>
       </c>
       <c r="J73" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="K73" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="L73" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M73" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="N73" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
@@ -4819,48 +4822,48 @@
         <v>14</v>
       </c>
       <c r="B74" t="s">
+        <v>400</v>
+      </c>
+      <c r="C74" t="s">
+        <v>401</v>
+      </c>
+      <c r="D74" t="s">
+        <v>80</v>
+      </c>
+      <c r="E74" t="s">
+        <v>402</v>
+      </c>
+      <c r="F74" t="s">
+        <v>402</v>
+      </c>
+      <c r="G74" t="s">
+        <v>397</v>
+      </c>
+      <c r="H74" t="s">
+        <v>402</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
+        <v>403</v>
+      </c>
+      <c r="K74" t="s">
+        <v>84</v>
+      </c>
+      <c r="L74" t="s">
         <v>399</v>
       </c>
-      <c r="C74" t="s">
-        <v>400</v>
-      </c>
-      <c r="D74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E74" t="s">
-        <v>401</v>
-      </c>
-      <c r="F74" t="s">
-        <v>401</v>
-      </c>
-      <c r="G74" t="s">
-        <v>396</v>
-      </c>
-      <c r="H74" t="s">
-        <v>401</v>
-      </c>
-      <c r="I74" t="s">
-        <v>20</v>
-      </c>
-      <c r="J74" t="s">
+      <c r="M74" t="s">
+        <v>255</v>
+      </c>
+      <c r="N74" t="s">
         <v>402</v>
-      </c>
-      <c r="K74" t="s">
-        <v>85</v>
-      </c>
-      <c r="L74" t="s">
-        <v>398</v>
-      </c>
-      <c r="M74" t="s">
-        <v>253</v>
-      </c>
-      <c r="N74" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/v2/BOM_4层非开发板版本_openups.xlsx
+++ b/hardware/v2/BOM_4层非开发板版本_openups.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-16" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-20" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -112,10 +112,10 @@
     <t>贴片电容(MLCC)</t>
   </si>
   <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>C1,C2,C3,C4,C12,C13,C14,C18,C19,C20,C26,C27,C28,C29,C30,C31,C32,C33,C41,C43,C44,C45,C47,C48</t>
+    <t>23</t>
+  </si>
+  <si>
+    <t>C1,C2,C3,C4,C12,C13,C14,C18,C19,C20,C26,C27,C28,C29,C30,C31,C32,C33,C41,C44,C45,C47,C48</t>
   </si>
   <si>
     <t>100nF</t>
@@ -148,7 +148,10 @@
     <t>C6119852</t>
   </si>
   <si>
-    <t>C7,C16</t>
+    <t>3</t>
+  </si>
+  <si>
+    <t>C7,C16,C43</t>
   </si>
   <si>
     <t>47nF</t>
@@ -389,9 +392,6 @@
   </si>
   <si>
     <t>肖特基二极管</t>
-  </si>
-  <si>
-    <t>3</t>
   </si>
   <si>
     <t>D3,D4</t>
@@ -1827,34 +1827,34 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" t="s">
         <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K6" t="s">
         <v>31</v>
@@ -1866,7 +1866,7 @@
         <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1874,31 +1874,31 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G7" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" t="s">
         <v>52</v>
       </c>
-      <c r="H7" t="s">
-        <v>51</v>
-      </c>
       <c r="I7" t="s">
         <v>20</v>
       </c>
       <c r="J7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K7" t="s">
         <v>31</v>
@@ -1910,7 +1910,7 @@
         <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1918,31 +1918,31 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>31</v>
@@ -1954,7 +1954,7 @@
         <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1962,31 +1962,31 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I9" t="s">
         <v>20</v>
       </c>
       <c r="J9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K9" t="s">
         <v>31</v>
@@ -1998,7 +1998,7 @@
         <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2006,31 +2006,31 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I10" t="s">
         <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
@@ -2042,7 +2042,7 @@
         <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2050,31 +2050,31 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I11" t="s">
         <v>20</v>
       </c>
       <c r="J11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>31</v>
@@ -2086,7 +2086,7 @@
         <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2094,31 +2094,31 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K12" t="s">
         <v>31</v>
@@ -2130,7 +2130,7 @@
         <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2138,31 +2138,31 @@
         <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" t="s">
         <v>29</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I13" t="s">
         <v>20</v>
       </c>
       <c r="J13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K13" t="s">
         <v>31</v>
@@ -2174,7 +2174,7 @@
         <v>24</v>
       </c>
       <c r="N13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2182,43 +2182,43 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G14" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" t="s">
         <v>82</v>
       </c>
-      <c r="H14" t="s">
-        <v>81</v>
-      </c>
       <c r="I14" t="s">
         <v>20</v>
       </c>
       <c r="J14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K14" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2226,43 +2226,43 @@
         <v>24</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
       </c>
       <c r="J15" t="s">
+        <v>91</v>
+      </c>
+      <c r="K15" t="s">
+        <v>85</v>
+      </c>
+      <c r="L15" t="s">
+        <v>86</v>
+      </c>
+      <c r="M15" t="s">
+        <v>24</v>
+      </c>
+      <c r="N15" t="s">
         <v>90</v>
-      </c>
-      <c r="K15" t="s">
-        <v>84</v>
-      </c>
-      <c r="L15" t="s">
-        <v>85</v>
-      </c>
-      <c r="M15" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2270,43 +2270,43 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G16" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" t="s">
         <v>94</v>
       </c>
-      <c r="H16" t="s">
-        <v>93</v>
-      </c>
       <c r="I16" t="s">
         <v>20</v>
       </c>
       <c r="J16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K16" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2314,43 +2314,43 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" t="s">
         <v>102</v>
       </c>
-      <c r="H17" t="s">
-        <v>101</v>
-      </c>
       <c r="I17" t="s">
         <v>20</v>
       </c>
       <c r="J17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2358,43 +2358,43 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G18" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" t="s">
         <v>108</v>
       </c>
-      <c r="H18" t="s">
-        <v>107</v>
-      </c>
       <c r="I18" t="s">
         <v>20</v>
       </c>
       <c r="J18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K18" t="s">
         <v>31</v>
       </c>
       <c r="L18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M18" t="s">
         <v>24</v>
       </c>
       <c r="N18" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2402,43 +2402,43 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" t="s">
+        <v>116</v>
+      </c>
+      <c r="H19" t="s">
         <v>114</v>
       </c>
-      <c r="G19" t="s">
-        <v>115</v>
-      </c>
-      <c r="H19" t="s">
-        <v>113</v>
-      </c>
       <c r="I19" t="s">
         <v>20</v>
       </c>
       <c r="J19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s">
         <v>24</v>
       </c>
       <c r="N19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2446,43 +2446,43 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G20" t="s">
+        <v>123</v>
+      </c>
+      <c r="H20" t="s">
         <v>122</v>
       </c>
-      <c r="H20" t="s">
-        <v>121</v>
-      </c>
       <c r="I20" t="s">
         <v>20</v>
       </c>
       <c r="J20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L20" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M20" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="N20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2496,7 +2496,7 @@
         <v>128</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E21" t="s">
         <v>129</v>
@@ -2505,7 +2505,7 @@
         <v>130</v>
       </c>
       <c r="G21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H21" t="s">
         <v>129</v>
@@ -2517,10 +2517,10 @@
         <v>131</v>
       </c>
       <c r="K21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M21" t="s">
         <v>24</v>
@@ -2540,7 +2540,7 @@
         <v>133</v>
       </c>
       <c r="D22" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E22" t="s">
         <v>134</v>
@@ -2561,13 +2561,13 @@
         <v>136</v>
       </c>
       <c r="K22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L22" t="s">
         <v>137</v>
       </c>
       <c r="M22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N22" t="s">
         <v>134</v>
@@ -2584,7 +2584,7 @@
         <v>139</v>
       </c>
       <c r="D23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E23" t="s">
         <v>140</v>
@@ -2593,7 +2593,7 @@
         <v>140</v>
       </c>
       <c r="G23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" t="s">
         <v>140</v>
@@ -2605,13 +2605,13 @@
         <v>141</v>
       </c>
       <c r="K23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L23" t="s">
         <v>142</v>
       </c>
       <c r="M23" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N23" t="s">
         <v>140</v>
@@ -2628,7 +2628,7 @@
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E24" t="s">
         <v>145</v>
@@ -2649,13 +2649,13 @@
         <v>147</v>
       </c>
       <c r="K24" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L24" t="s">
         <v>148</v>
       </c>
       <c r="M24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N24" t="s">
         <v>145</v>
@@ -2760,7 +2760,7 @@
         <v>163</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
         <v>164</v>
@@ -2804,7 +2804,7 @@
         <v>170</v>
       </c>
       <c r="D28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E28" t="s">
         <v>171</v>
@@ -2848,7 +2848,7 @@
         <v>174</v>
       </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" t="s">
         <v>175</v>
@@ -2892,7 +2892,7 @@
         <v>178</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E30" t="s">
         <v>179</v>
@@ -2919,7 +2919,7 @@
         <v>168</v>
       </c>
       <c r="M30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N30" t="s">
         <v>179</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
         <v>182</v>
@@ -2936,7 +2936,7 @@
         <v>183</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E31" t="s">
         <v>184</v>
@@ -2957,7 +2957,7 @@
         <v>186</v>
       </c>
       <c r="K31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s">
         <v>187</v>
@@ -2971,7 +2971,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
         <v>189</v>
@@ -2980,7 +2980,7 @@
         <v>190</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E32" t="s">
         <v>191</v>
@@ -3001,7 +3001,7 @@
         <v>193</v>
       </c>
       <c r="K32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L32" t="s">
         <v>187</v>
@@ -3024,7 +3024,7 @@
         <v>196</v>
       </c>
       <c r="D33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" t="s">
         <v>197</v>
@@ -3045,13 +3045,13 @@
         <v>199</v>
       </c>
       <c r="K33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M33" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="N33" t="s">
         <v>197</v>
@@ -3068,7 +3068,7 @@
         <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" t="s">
         <v>202</v>
@@ -3077,7 +3077,7 @@
         <v>203</v>
       </c>
       <c r="G34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H34" t="s">
         <v>202</v>
@@ -3089,13 +3089,13 @@
         <v>204</v>
       </c>
       <c r="K34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L34" t="s">
         <v>187</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="N34" t="s">
         <v>202</v>
@@ -3112,7 +3112,7 @@
         <v>206</v>
       </c>
       <c r="D35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E35" t="s">
         <v>207</v>
@@ -3133,13 +3133,13 @@
         <v>209</v>
       </c>
       <c r="K35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L35" t="s">
         <v>187</v>
       </c>
       <c r="M35" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="N35" t="s">
         <v>207</v>
@@ -3279,7 +3279,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B39" t="s">
         <v>226</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
         <v>234</v>
@@ -3869,7 +3869,7 @@
         <v>283</v>
       </c>
       <c r="G52" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H52" t="s">
         <v>283</v>
@@ -3895,7 +3895,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B53" t="s">
         <v>286</v>
@@ -4036,7 +4036,7 @@
         <v>211</v>
       </c>
       <c r="D56" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E56" t="s">
         <v>300</v>
@@ -4045,7 +4045,7 @@
         <v>300</v>
       </c>
       <c r="G56" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H56" t="s">
         <v>300</v>
@@ -4309,7 +4309,7 @@
         <v>327</v>
       </c>
       <c r="G62" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H62" t="s">
         <v>327</v>
@@ -4353,7 +4353,7 @@
         <v>331</v>
       </c>
       <c r="G63" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H63" t="s">
         <v>331</v>
@@ -4379,7 +4379,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
         <v>333</v>
@@ -4388,7 +4388,7 @@
         <v>334</v>
       </c>
       <c r="D64" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E64" t="s">
         <v>335</v>
@@ -4415,7 +4415,7 @@
         <v>339</v>
       </c>
       <c r="M64" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N64" t="s">
         <v>335</v>
@@ -4432,7 +4432,7 @@
         <v>341</v>
       </c>
       <c r="D65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E65" t="s">
         <v>342</v>
@@ -4453,10 +4453,10 @@
         <v>344</v>
       </c>
       <c r="K65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L65" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M65" t="s">
         <v>345</v>
@@ -4476,7 +4476,7 @@
         <v>347</v>
       </c>
       <c r="D66" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E66" t="s">
         <v>348</v>
@@ -4520,7 +4520,7 @@
         <v>354</v>
       </c>
       <c r="D67" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E67" t="s">
         <v>355</v>
@@ -4547,7 +4547,7 @@
         <v>359</v>
       </c>
       <c r="M67" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N67" t="s">
         <v>355</v>
@@ -4564,7 +4564,7 @@
         <v>361</v>
       </c>
       <c r="D68" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E68" t="s">
         <v>362</v>
@@ -4608,7 +4608,7 @@
         <v>367</v>
       </c>
       <c r="D69" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E69" t="s">
         <v>368</v>
@@ -4635,7 +4635,7 @@
         <v>372</v>
       </c>
       <c r="M69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N69" t="s">
         <v>368</v>
@@ -4652,7 +4652,7 @@
         <v>374</v>
       </c>
       <c r="D70" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E70" t="s">
         <v>375</v>
@@ -4696,7 +4696,7 @@
         <v>380</v>
       </c>
       <c r="D71" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E71" t="s">
         <v>381</v>
@@ -4740,7 +4740,7 @@
         <v>388</v>
       </c>
       <c r="D72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E72" t="s">
         <v>389</v>
@@ -4784,7 +4784,7 @@
         <v>395</v>
       </c>
       <c r="D73" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E73" t="s">
         <v>396</v>
@@ -4805,13 +4805,13 @@
         <v>398</v>
       </c>
       <c r="K73" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L73" t="s">
         <v>399</v>
       </c>
       <c r="M73" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N73" t="s">
         <v>396</v>
@@ -4828,7 +4828,7 @@
         <v>401</v>
       </c>
       <c r="D74" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E74" t="s">
         <v>402</v>
@@ -4849,7 +4849,7 @@
         <v>403</v>
       </c>
       <c r="K74" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L74" t="s">
         <v>399</v>
@@ -4863,7 +4863,7 @@
     </row>
     <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/hardware/v2/BOM_4层非开发板版本_openups.xlsx
+++ b/hardware/v2/BOM_4层非开发板版本_openups.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-20" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="BOM_4层非开发板版本_2026-05-25" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -148,97 +148,97 @@
     <t>C6119852</t>
   </si>
   <si>
+    <t>C7,C16</t>
+  </si>
+  <si>
+    <t>47nF</t>
+  </si>
+  <si>
+    <t>CL10B473KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1622</t>
+  </si>
+  <si>
+    <t>C8,C9,C24,C25,C46</t>
+  </si>
+  <si>
+    <t>10uF</t>
+  </si>
+  <si>
+    <t>CGA0603X5R106K100JT,CL10A106MA8NRNC</t>
+  </si>
+  <si>
+    <t>HRE(芯声),SAMSUNG(三星)</t>
+  </si>
+  <si>
+    <t>C96446,C6119842</t>
+  </si>
+  <si>
+    <t>C10,C11,C15,C38,C40</t>
+  </si>
+  <si>
+    <t>100pF</t>
+  </si>
+  <si>
+    <t>CL10C101JB8NNNC</t>
+  </si>
+  <si>
+    <t>C14858</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>1nF</t>
+  </si>
+  <si>
+    <t>CL10B102KB8NNNC</t>
+  </si>
+  <si>
+    <t>C1588</t>
+  </si>
+  <si>
+    <t>C21,C22</t>
+  </si>
+  <si>
+    <t>22uF</t>
+  </si>
+  <si>
+    <t>CL10A226MP8NUNE</t>
+  </si>
+  <si>
+    <t>C86295</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>33pF</t>
+  </si>
+  <si>
+    <t>CL10C330JB8NNNC</t>
+  </si>
+  <si>
+    <t>C1663</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>CGA0603X5R475K250JT</t>
+  </si>
+  <si>
+    <t>C6119856</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>C7,C16,C43</t>
-  </si>
-  <si>
-    <t>47nF</t>
-  </si>
-  <si>
-    <t>CL10B473KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1622</t>
-  </si>
-  <si>
-    <t>C8,C9,C24,C25,C46</t>
-  </si>
-  <si>
-    <t>10uF</t>
-  </si>
-  <si>
-    <t>CGA0603X5R106K100JT,CL10A106MA8NRNC</t>
-  </si>
-  <si>
-    <t>HRE(芯声),SAMSUNG(三星)</t>
-  </si>
-  <si>
-    <t>C96446,C6119842</t>
-  </si>
-  <si>
-    <t>C10,C11,C15,C38,C40</t>
-  </si>
-  <si>
-    <t>100pF</t>
-  </si>
-  <si>
-    <t>CL10C101JB8NNNC</t>
-  </si>
-  <si>
-    <t>C14858</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>1nF</t>
-  </si>
-  <si>
-    <t>CL10B102KB8NNNC</t>
-  </si>
-  <si>
-    <t>C1588</t>
-  </si>
-  <si>
-    <t>C21,C22</t>
-  </si>
-  <si>
-    <t>22uF</t>
-  </si>
-  <si>
-    <t>CL10A226MP8NUNE</t>
-  </si>
-  <si>
-    <t>C86295</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>33pF</t>
-  </si>
-  <si>
-    <t>CL10C330JB8NNNC</t>
-  </si>
-  <si>
-    <t>C1663</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>CGA0603X5R475K250JT</t>
-  </si>
-  <si>
-    <t>C6119856</t>
-  </si>
-  <si>
-    <t>C39,C42</t>
+    <t>C39,C42,C43</t>
   </si>
   <si>
     <t>10nF</t>
@@ -277,7 +277,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>CN2,CN6</t>
+    <t>CN2</t>
   </si>
   <si>
     <t>CONN-TH_HX-XH2.54-2PWZ</t>
@@ -1827,34 +1827,34 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s">
         <v>45</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
       <c r="D6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
         <v>47</v>
-      </c>
-      <c r="E6" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" t="s">
-        <v>48</v>
       </c>
       <c r="G6" t="s">
         <v>29</v>
       </c>
       <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" t="s">
         <v>48</v>
-      </c>
-      <c r="I6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J6" t="s">
-        <v>49</v>
       </c>
       <c r="K6" t="s">
         <v>31</v>
@@ -1866,7 +1866,7 @@
         <v>24</v>
       </c>
       <c r="N6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1874,31 +1874,31 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7" t="s">
         <v>51</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" t="s">
         <v>51</v>
       </c>
-      <c r="F7" t="s">
-        <v>52</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J7" t="s">
         <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>54</v>
       </c>
       <c r="K7" t="s">
         <v>31</v>
@@ -1910,7 +1910,7 @@
         <v>24</v>
       </c>
       <c r="N7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1918,31 +1918,31 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
         <v>26</v>
       </c>
       <c r="D8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
         <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" t="s">
-        <v>57</v>
       </c>
       <c r="G8" t="s">
         <v>29</v>
       </c>
       <c r="H8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" t="s">
         <v>57</v>
-      </c>
-      <c r="I8" t="s">
-        <v>20</v>
-      </c>
-      <c r="J8" t="s">
-        <v>58</v>
       </c>
       <c r="K8" t="s">
         <v>31</v>
@@ -1954,7 +1954,7 @@
         <v>24</v>
       </c>
       <c r="N8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1962,31 +1962,31 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>26</v>
       </c>
       <c r="D9" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
         <v>60</v>
-      </c>
-      <c r="E9" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
       </c>
       <c r="G9" t="s">
         <v>29</v>
       </c>
       <c r="H9" t="s">
+        <v>60</v>
+      </c>
+      <c r="I9" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" t="s">
         <v>61</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" t="s">
-        <v>62</v>
       </c>
       <c r="K9" t="s">
         <v>31</v>
@@ -1998,7 +1998,7 @@
         <v>24</v>
       </c>
       <c r="N9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2006,31 +2006,31 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
         <v>26</v>
       </c>
       <c r="D10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" t="s">
         <v>64</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="s">
-        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
       </c>
       <c r="H10" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" t="s">
         <v>65</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J10" t="s">
-        <v>66</v>
       </c>
       <c r="K10" t="s">
         <v>31</v>
@@ -2042,7 +2042,7 @@
         <v>24</v>
       </c>
       <c r="N10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2050,31 +2050,31 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
         <v>26</v>
       </c>
       <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" t="s">
         <v>68</v>
-      </c>
-      <c r="E11" t="s">
-        <v>68</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
       </c>
       <c r="G11" t="s">
         <v>29</v>
       </c>
       <c r="H11" t="s">
+        <v>68</v>
+      </c>
+      <c r="I11" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" t="s">
         <v>69</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>70</v>
       </c>
       <c r="K11" t="s">
         <v>31</v>
@@ -2086,7 +2086,7 @@
         <v>24</v>
       </c>
       <c r="N11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2094,31 +2094,31 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
         <v>72</v>
-      </c>
-      <c r="E12" t="s">
-        <v>72</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
       </c>
       <c r="G12" t="s">
         <v>43</v>
       </c>
       <c r="H12" t="s">
+        <v>72</v>
+      </c>
+      <c r="I12" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" t="s">
         <v>73</v>
-      </c>
-      <c r="I12" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" t="s">
-        <v>74</v>
       </c>
       <c r="K12" t="s">
         <v>31</v>
@@ -2130,12 +2130,12 @@
         <v>24</v>
       </c>
       <c r="N12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>75</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>88</v>
@@ -2479,7 +2479,7 @@
         <v>126</v>
       </c>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
         <v>122</v>
@@ -2927,7 +2927,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
         <v>182</v>
@@ -3051,7 +3051,7 @@
         <v>81</v>
       </c>
       <c r="M33" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N33" t="s">
         <v>197</v>
@@ -3095,7 +3095,7 @@
         <v>187</v>
       </c>
       <c r="M34" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N34" t="s">
         <v>202</v>
@@ -3139,7 +3139,7 @@
         <v>187</v>
       </c>
       <c r="M35" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="N35" t="s">
         <v>207</v>
@@ -3367,7 +3367,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="B41" t="s">
         <v>234</v>
